--- a/입시결과.xlsx
+++ b/입시결과.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\02_Analysis\01_2024_Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A78D943-32C9-4FE5-8203-BC1D48BFB4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3077A0-E7D7-482B-991D-1C89CD1E1420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-10365" windowWidth="16440" windowHeight="28320" xr2:uid="{5F448DE1-2C11-4C28-BE33-0B2F9FFA91F2}"/>
   </bookViews>
@@ -21989,7 +21989,7 @@
         <v>153</v>
       </c>
       <c r="F572">
-        <v>3.448</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="G572">
         <v>3</v>
@@ -22024,7 +22024,7 @@
         <v>153</v>
       </c>
       <c r="F573">
-        <v>3.448</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="G573">
         <v>3</v>
@@ -22059,7 +22059,7 @@
         <v>518</v>
       </c>
       <c r="F574">
-        <v>3.448</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="G574">
         <v>3</v>
@@ -22094,7 +22094,7 @@
         <v>519</v>
       </c>
       <c r="F575">
-        <v>3.448</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="G575">
         <v>3</v>
@@ -22129,7 +22129,7 @@
         <v>160</v>
       </c>
       <c r="F576">
-        <v>3.448</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="G576">
         <v>3</v>
@@ -22164,7 +22164,7 @@
         <v>520</v>
       </c>
       <c r="F577">
-        <v>3.448</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="G577">
         <v>3</v>
@@ -22199,7 +22199,7 @@
         <v>325</v>
       </c>
       <c r="F578">
-        <v>3.448</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="G578">
         <v>3</v>
@@ -22234,7 +22234,7 @@
         <v>521</v>
       </c>
       <c r="F579">
-        <v>3.448</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="G579">
         <v>3</v>
@@ -22269,7 +22269,7 @@
         <v>325</v>
       </c>
       <c r="F580">
-        <v>3.448</v>
+        <v>3.6040000000000001</v>
       </c>
       <c r="G580">
         <v>3</v>
@@ -22304,7 +22304,7 @@
         <v>145</v>
       </c>
       <c r="F581">
-        <v>6.1059999999999999</v>
+        <v>6.1719999999999997</v>
       </c>
       <c r="G581">
         <v>6</v>
@@ -22339,7 +22339,7 @@
         <v>523</v>
       </c>
       <c r="F582">
-        <v>6.1059999999999999</v>
+        <v>6.1719999999999997</v>
       </c>
       <c r="G582">
         <v>6</v>
@@ -22374,7 +22374,7 @@
         <v>177</v>
       </c>
       <c r="F583">
-        <v>6.1059999999999999</v>
+        <v>6.1719999999999997</v>
       </c>
       <c r="G583">
         <v>6</v>
@@ -22409,7 +22409,7 @@
         <v>249</v>
       </c>
       <c r="F584">
-        <v>5.3920000000000003</v>
+        <v>5.3949999999999996</v>
       </c>
     </row>
     <row r="585" spans="1:11" x14ac:dyDescent="0.3">
@@ -22429,7 +22429,7 @@
         <v>73</v>
       </c>
       <c r="F585">
-        <v>5.3920000000000003</v>
+        <v>5.3949999999999996</v>
       </c>
     </row>
     <row r="586" spans="1:11" x14ac:dyDescent="0.3">
@@ -22449,7 +22449,7 @@
         <v>325</v>
       </c>
       <c r="F586">
-        <v>5.3920000000000003</v>
+        <v>5.3949999999999996</v>
       </c>
     </row>
     <row r="587" spans="1:11" x14ac:dyDescent="0.3">
@@ -22469,7 +22469,7 @@
         <v>524</v>
       </c>
       <c r="F587">
-        <v>5.3920000000000003</v>
+        <v>5.3949999999999996</v>
       </c>
     </row>
     <row r="588" spans="1:11" x14ac:dyDescent="0.3">
@@ -22489,7 +22489,7 @@
         <v>525</v>
       </c>
       <c r="F588">
-        <v>6.3710000000000004</v>
+        <v>6.4269999999999996</v>
       </c>
     </row>
     <row r="589" spans="1:11" x14ac:dyDescent="0.3">
@@ -22509,7 +22509,7 @@
         <v>525</v>
       </c>
       <c r="F589">
-        <v>6.3710000000000004</v>
+        <v>6.4269999999999996</v>
       </c>
     </row>
     <row r="590" spans="1:11" x14ac:dyDescent="0.3">
@@ -22529,7 +22529,7 @@
         <v>526</v>
       </c>
       <c r="F590">
-        <v>2.1680000000000001</v>
+        <v>2.161</v>
       </c>
       <c r="G590">
         <v>4</v>
@@ -22564,7 +22564,7 @@
         <v>295</v>
       </c>
       <c r="F591">
-        <v>5.0640000000000001</v>
+        <v>5.2329999999999997</v>
       </c>
       <c r="G591">
         <v>5</v>
@@ -22599,7 +22599,7 @@
         <v>331</v>
       </c>
       <c r="F592">
-        <v>1.097</v>
+        <v>1.075</v>
       </c>
       <c r="G592">
         <v>2</v>
@@ -22634,7 +22634,7 @@
         <v>527</v>
       </c>
       <c r="F593">
-        <v>1.097</v>
+        <v>1.075</v>
       </c>
       <c r="G593">
         <v>2</v>
@@ -22669,7 +22669,7 @@
         <v>107</v>
       </c>
       <c r="F594">
-        <v>1.097</v>
+        <v>1.075</v>
       </c>
       <c r="G594">
         <v>2</v>
@@ -22704,7 +22704,7 @@
         <v>528</v>
       </c>
       <c r="F595">
-        <v>2.8879999999999999</v>
+        <v>2.7240000000000002</v>
       </c>
       <c r="G595">
         <v>3</v>
@@ -22739,7 +22739,7 @@
         <v>529</v>
       </c>
       <c r="F596">
-        <v>2.8879999999999999</v>
+        <v>2.7240000000000002</v>
       </c>
       <c r="G596">
         <v>3</v>
@@ -22774,7 +22774,7 @@
         <v>328</v>
       </c>
       <c r="F597">
-        <v>3.0089999999999999</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="G597">
         <v>4</v>
@@ -22809,7 +22809,7 @@
         <v>328</v>
       </c>
       <c r="F598">
-        <v>3.0089999999999999</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="G598">
         <v>4</v>
@@ -22844,7 +22844,7 @@
         <v>530</v>
       </c>
       <c r="F599">
-        <v>6.9569999999999999</v>
+        <v>6.9690000000000003</v>
       </c>
       <c r="G599">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>531</v>
       </c>
       <c r="F600">
-        <v>6.9569999999999999</v>
+        <v>6.9690000000000003</v>
       </c>
       <c r="G600">
         <v>9</v>
@@ -22914,7 +22914,7 @@
         <v>532</v>
       </c>
       <c r="F601">
-        <v>8.7100000000000009</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="602" spans="1:11" x14ac:dyDescent="0.3">
@@ -22934,7 +22934,7 @@
         <v>533</v>
       </c>
       <c r="F602">
-        <v>4.3</v>
+        <v>4.2110000000000003</v>
       </c>
       <c r="G602">
         <v>4</v>
@@ -22969,7 +22969,7 @@
         <v>534</v>
       </c>
       <c r="F603">
-        <v>3.5609999999999999</v>
+        <v>3.4830000000000001</v>
       </c>
       <c r="G603">
         <v>3</v>
@@ -23004,7 +23004,7 @@
         <v>535</v>
       </c>
       <c r="F604">
-        <v>7.6120000000000001</v>
+        <v>7.4870000000000001</v>
       </c>
       <c r="G604">
         <v>8</v>
@@ -23030,7 +23030,7 @@
         <v>303</v>
       </c>
       <c r="F605">
-        <v>7.6120000000000001</v>
+        <v>7.4870000000000001</v>
       </c>
       <c r="G605">
         <v>8</v>
@@ -23056,7 +23056,7 @@
         <v>536</v>
       </c>
       <c r="F606">
-        <v>7.6120000000000001</v>
+        <v>7.4870000000000001</v>
       </c>
       <c r="G606">
         <v>8</v>
@@ -23082,7 +23082,7 @@
         <v>431</v>
       </c>
       <c r="F607">
-        <v>5.1470000000000002</v>
+        <v>5.3440000000000003</v>
       </c>
       <c r="G607">
         <v>5</v>
@@ -23117,7 +23117,7 @@
         <v>537</v>
       </c>
       <c r="F608">
-        <v>6.5819999999999999</v>
+        <v>6.4669999999999996</v>
       </c>
       <c r="G608">
         <v>6</v>
@@ -23152,7 +23152,7 @@
         <v>538</v>
       </c>
       <c r="F609">
-        <v>6.9720000000000004</v>
+        <v>6.9889999999999999</v>
       </c>
       <c r="G609">
         <v>7</v>
@@ -23187,7 +23187,7 @@
         <v>539</v>
       </c>
       <c r="F610">
-        <v>4.7089999999999996</v>
+        <v>4.7110000000000003</v>
       </c>
       <c r="G610">
         <v>5</v>
@@ -23222,7 +23222,7 @@
         <v>144</v>
       </c>
       <c r="F611">
-        <v>4.7089999999999996</v>
+        <v>4.7110000000000003</v>
       </c>
       <c r="G611">
         <v>5</v>
@@ -23257,7 +23257,7 @@
         <v>540</v>
       </c>
       <c r="F612">
-        <v>4.7089999999999996</v>
+        <v>4.7110000000000003</v>
       </c>
       <c r="G612">
         <v>5</v>
@@ -23292,7 +23292,7 @@
         <v>328</v>
       </c>
       <c r="F613">
-        <v>5.6280000000000001</v>
+        <v>5.72</v>
       </c>
       <c r="G613">
         <v>7</v>
@@ -23327,7 +23327,7 @@
         <v>541</v>
       </c>
       <c r="F614">
-        <v>5.6280000000000001</v>
+        <v>5.72</v>
       </c>
       <c r="G614">
         <v>7</v>
@@ -23362,7 +23362,7 @@
         <v>308</v>
       </c>
       <c r="F615">
-        <v>6.2569999999999997</v>
+        <v>6.4409999999999998</v>
       </c>
       <c r="G615">
         <v>6</v>
@@ -23397,7 +23397,7 @@
         <v>303</v>
       </c>
       <c r="F616">
-        <v>6.2569999999999997</v>
+        <v>6.4409999999999998</v>
       </c>
       <c r="G616">
         <v>6</v>
@@ -23432,7 +23432,7 @@
         <v>303</v>
       </c>
       <c r="F617">
-        <v>6.2569999999999997</v>
+        <v>6.4409999999999998</v>
       </c>
       <c r="G617">
         <v>6</v>
@@ -23467,7 +23467,7 @@
         <v>303</v>
       </c>
       <c r="F618">
-        <v>6.2569999999999997</v>
+        <v>6.4409999999999998</v>
       </c>
       <c r="G618">
         <v>6</v>
@@ -23502,7 +23502,7 @@
         <v>303</v>
       </c>
       <c r="F619">
-        <v>6.2569999999999997</v>
+        <v>6.4409999999999998</v>
       </c>
       <c r="G619">
         <v>6</v>
@@ -23537,7 +23537,7 @@
         <v>543</v>
       </c>
       <c r="F620">
-        <v>3.8319999999999999</v>
+        <v>3.8170000000000002</v>
       </c>
       <c r="G620">
         <v>5</v>
@@ -23569,7 +23569,7 @@
         <v>173</v>
       </c>
       <c r="F621">
-        <v>3.8319999999999999</v>
+        <v>3.8170000000000002</v>
       </c>
       <c r="G621">
         <v>5</v>
@@ -23601,7 +23601,7 @@
         <v>544</v>
       </c>
       <c r="F622">
-        <v>3.8319999999999999</v>
+        <v>3.8170000000000002</v>
       </c>
       <c r="G622">
         <v>5</v>
@@ -23633,7 +23633,7 @@
         <v>543</v>
       </c>
       <c r="F623">
-        <v>3.8319999999999999</v>
+        <v>3.8170000000000002</v>
       </c>
       <c r="G623">
         <v>5</v>
@@ -23665,7 +23665,7 @@
         <v>445</v>
       </c>
       <c r="F624">
-        <v>4.7640000000000002</v>
+        <v>4.8220000000000001</v>
       </c>
       <c r="G624">
         <v>5</v>
@@ -23700,7 +23700,7 @@
         <v>199</v>
       </c>
       <c r="F625">
-        <v>4.7640000000000002</v>
+        <v>4.8220000000000001</v>
       </c>
       <c r="G625">
         <v>5</v>
@@ -23735,7 +23735,7 @@
         <v>275</v>
       </c>
       <c r="F626">
-        <v>4.7640000000000002</v>
+        <v>4.8220000000000001</v>
       </c>
       <c r="G626">
         <v>5</v>
@@ -23770,7 +23770,7 @@
         <v>545</v>
       </c>
       <c r="F627">
-        <v>4.7640000000000002</v>
+        <v>4.8220000000000001</v>
       </c>
       <c r="G627">
         <v>5</v>
@@ -23805,7 +23805,7 @@
         <v>173</v>
       </c>
       <c r="F628">
-        <v>4.7640000000000002</v>
+        <v>4.8220000000000001</v>
       </c>
       <c r="G628">
         <v>5</v>
@@ -23840,7 +23840,7 @@
         <v>546</v>
       </c>
       <c r="F629">
-        <v>1.3089999999999999</v>
+        <v>1.333</v>
       </c>
       <c r="G629">
         <v>1</v>
@@ -23875,7 +23875,7 @@
         <v>37</v>
       </c>
       <c r="F630">
-        <v>1.3089999999999999</v>
+        <v>1.333</v>
       </c>
       <c r="G630">
         <v>1</v>
@@ -23910,7 +23910,7 @@
         <v>547</v>
       </c>
       <c r="F631">
-        <v>1.3089999999999999</v>
+        <v>1.333</v>
       </c>
       <c r="G631">
         <v>1</v>
@@ -23945,7 +23945,7 @@
         <v>547</v>
       </c>
       <c r="F632">
-        <v>1.3089999999999999</v>
+        <v>1.333</v>
       </c>
       <c r="G632">
         <v>1</v>
@@ -23980,7 +23980,7 @@
         <v>80</v>
       </c>
       <c r="F633">
-        <v>1.3089999999999999</v>
+        <v>1.333</v>
       </c>
       <c r="G633">
         <v>1</v>
@@ -24015,7 +24015,7 @@
         <v>547</v>
       </c>
       <c r="F634">
-        <v>1.3089999999999999</v>
+        <v>1.333</v>
       </c>
       <c r="G634">
         <v>1</v>
@@ -24050,7 +24050,7 @@
         <v>107</v>
       </c>
       <c r="F635">
-        <v>4.8410000000000002</v>
+        <v>4.7590000000000003</v>
       </c>
     </row>
     <row r="636" spans="1:11" x14ac:dyDescent="0.3">
@@ -24070,7 +24070,7 @@
         <v>548</v>
       </c>
       <c r="F636">
-        <v>4.8410000000000002</v>
+        <v>4.7590000000000003</v>
       </c>
     </row>
     <row r="637" spans="1:11" x14ac:dyDescent="0.3">
@@ -24090,7 +24090,7 @@
         <v>524</v>
       </c>
       <c r="F637">
-        <v>2.2829999999999999</v>
+        <v>2.3010000000000002</v>
       </c>
       <c r="G637">
         <v>5</v>
@@ -24125,7 +24125,7 @@
         <v>549</v>
       </c>
       <c r="F638">
-        <v>2.2829999999999999</v>
+        <v>2.3010000000000002</v>
       </c>
       <c r="G638">
         <v>5</v>
@@ -24160,7 +24160,7 @@
         <v>51</v>
       </c>
       <c r="F639">
-        <v>2.2829999999999999</v>
+        <v>2.3010000000000002</v>
       </c>
       <c r="G639">
         <v>5</v>
@@ -24195,7 +24195,7 @@
         <v>153</v>
       </c>
       <c r="F640">
-        <v>4.0640000000000001</v>
+        <v>4.1219999999999999</v>
       </c>
       <c r="G640">
         <v>5</v>
@@ -24230,7 +24230,7 @@
         <v>550</v>
       </c>
       <c r="F641">
-        <v>7.5490000000000004</v>
+        <v>7.5590000000000002</v>
       </c>
       <c r="G641">
         <v>7</v>
@@ -24265,7 +24265,7 @@
         <v>551</v>
       </c>
       <c r="F642">
-        <v>3.1240000000000001</v>
+        <v>3.0430000000000001</v>
       </c>
       <c r="G642">
         <v>4</v>
@@ -24300,7 +24300,7 @@
         <v>49</v>
       </c>
       <c r="F643">
-        <v>2.319</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="G643">
         <v>3</v>
@@ -24335,7 +24335,7 @@
         <v>552</v>
       </c>
       <c r="F644">
-        <v>6.2919999999999998</v>
+        <v>6.29</v>
       </c>
       <c r="G644">
         <v>8</v>
@@ -24370,7 +24370,7 @@
         <v>553</v>
       </c>
       <c r="F645">
-        <v>6.2919999999999998</v>
+        <v>6.29</v>
       </c>
       <c r="G645">
         <v>8</v>
@@ -24405,7 +24405,7 @@
         <v>554</v>
       </c>
       <c r="F646">
-        <v>6.2919999999999998</v>
+        <v>6.29</v>
       </c>
       <c r="G646">
         <v>8</v>
@@ -24440,7 +24440,7 @@
         <v>555</v>
       </c>
       <c r="F647">
-        <v>6.2919999999999998</v>
+        <v>6.29</v>
       </c>
       <c r="G647">
         <v>8</v>
@@ -24475,7 +24475,7 @@
         <v>556</v>
       </c>
       <c r="F648">
-        <v>5.1210000000000004</v>
+        <v>5.149</v>
       </c>
       <c r="G648">
         <v>6</v>
@@ -24510,7 +24510,7 @@
         <v>398</v>
       </c>
       <c r="F649">
-        <v>5.1210000000000004</v>
+        <v>5.149</v>
       </c>
       <c r="G649">
         <v>6</v>
@@ -24545,7 +24545,7 @@
         <v>123</v>
       </c>
       <c r="F650">
-        <v>5.1210000000000004</v>
+        <v>5.149</v>
       </c>
       <c r="G650">
         <v>6</v>
@@ -24580,7 +24580,7 @@
         <v>557</v>
       </c>
       <c r="F651">
-        <v>5.274</v>
+        <v>5.2039999999999997</v>
       </c>
       <c r="G651">
         <v>6</v>
@@ -24615,7 +24615,7 @@
         <v>558</v>
       </c>
       <c r="F652">
-        <v>5.274</v>
+        <v>5.2039999999999997</v>
       </c>
       <c r="G652">
         <v>6</v>
@@ -24650,7 +24650,7 @@
         <v>559</v>
       </c>
       <c r="F653">
-        <v>5.274</v>
+        <v>5.2039999999999997</v>
       </c>
       <c r="G653">
         <v>6</v>
@@ -24685,7 +24685,7 @@
         <v>270</v>
       </c>
       <c r="F654">
-        <v>7.1820000000000004</v>
+        <v>7.1630000000000003</v>
       </c>
     </row>
     <row r="655" spans="1:11" x14ac:dyDescent="0.3">
@@ -24705,7 +24705,7 @@
         <v>560</v>
       </c>
       <c r="F655">
-        <v>5.5490000000000004</v>
+        <v>5.6020000000000003</v>
       </c>
       <c r="G655">
         <v>4</v>
@@ -24740,7 +24740,7 @@
         <v>153</v>
       </c>
       <c r="F656">
-        <v>5.5490000000000004</v>
+        <v>5.6020000000000003</v>
       </c>
       <c r="G656">
         <v>4</v>
@@ -24775,7 +24775,7 @@
         <v>153</v>
       </c>
       <c r="F657">
-        <v>5.5490000000000004</v>
+        <v>5.6020000000000003</v>
       </c>
       <c r="G657">
         <v>4</v>
@@ -24810,7 +24810,7 @@
         <v>73</v>
       </c>
       <c r="F658">
-        <v>6.218</v>
+        <v>6.2</v>
       </c>
       <c r="G658">
         <v>7</v>
@@ -24845,7 +24845,7 @@
         <v>560</v>
       </c>
       <c r="F659">
-        <v>6.218</v>
+        <v>6.2</v>
       </c>
       <c r="G659">
         <v>7</v>
@@ -24880,7 +24880,7 @@
         <v>458</v>
       </c>
       <c r="F660">
-        <v>3.77</v>
+        <v>3.7850000000000001</v>
       </c>
       <c r="G660">
         <v>5</v>
@@ -24915,7 +24915,7 @@
         <v>561</v>
       </c>
       <c r="F661">
-        <v>4.6449999999999996</v>
+        <v>4.8330000000000002</v>
       </c>
       <c r="G661">
         <v>4</v>
@@ -24950,7 +24950,7 @@
         <v>562</v>
       </c>
       <c r="F662">
-        <v>5.1589999999999998</v>
+        <v>5.149</v>
       </c>
       <c r="G662">
         <v>5</v>
@@ -24985,7 +24985,7 @@
         <v>563</v>
       </c>
       <c r="F663">
-        <v>5.1589999999999998</v>
+        <v>5.149</v>
       </c>
       <c r="G663">
         <v>5</v>
@@ -25020,7 +25020,7 @@
         <v>328</v>
       </c>
       <c r="F664">
-        <v>3.0089999999999999</v>
+        <v>2.9889999999999999</v>
       </c>
       <c r="G664">
         <v>3</v>
@@ -25055,7 +25055,7 @@
         <v>564</v>
       </c>
       <c r="F665">
-        <v>3.0089999999999999</v>
+        <v>2.9889999999999999</v>
       </c>
       <c r="G665">
         <v>3</v>
@@ -25090,7 +25090,7 @@
         <v>565</v>
       </c>
       <c r="F666">
-        <v>3.0089999999999999</v>
+        <v>2.9889999999999999</v>
       </c>
       <c r="G666">
         <v>3</v>
@@ -25125,7 +25125,7 @@
         <v>566</v>
       </c>
       <c r="F667">
-        <v>4.1859999999999999</v>
+        <v>4.226</v>
       </c>
       <c r="G667">
         <v>5</v>
@@ -25160,7 +25160,7 @@
         <v>567</v>
       </c>
       <c r="F668">
-        <v>4.1859999999999999</v>
+        <v>4.226</v>
       </c>
       <c r="G668">
         <v>5</v>
@@ -25195,7 +25195,7 @@
         <v>568</v>
       </c>
       <c r="F669">
-        <v>6.01</v>
+        <v>6.0129999999999999</v>
       </c>
       <c r="G669">
         <v>6</v>
@@ -25230,7 +25230,7 @@
         <v>569</v>
       </c>
       <c r="F670">
-        <v>3.1869999999999998</v>
+        <v>2.931</v>
       </c>
       <c r="G670">
         <v>4</v>
@@ -25265,7 +25265,7 @@
         <v>73</v>
       </c>
       <c r="F671">
-        <v>4.891</v>
+        <v>4.9180000000000001</v>
       </c>
       <c r="G671">
         <v>4</v>
@@ -25300,7 +25300,7 @@
         <v>73</v>
       </c>
       <c r="F672">
-        <v>4.891</v>
+        <v>4.867</v>
       </c>
       <c r="G672">
         <v>4</v>
@@ -25335,7 +25335,7 @@
         <v>73</v>
       </c>
       <c r="F673">
-        <v>4.891</v>
+        <v>4.867</v>
       </c>
       <c r="G673">
         <v>4</v>
@@ -25370,7 +25370,7 @@
         <v>547</v>
       </c>
       <c r="F674">
-        <v>1.587</v>
+        <v>1.512</v>
       </c>
       <c r="G674">
         <v>3</v>
@@ -25405,7 +25405,7 @@
         <v>571</v>
       </c>
       <c r="F675">
-        <v>1.587</v>
+        <v>1.512</v>
       </c>
       <c r="G675">
         <v>3</v>
@@ -25440,7 +25440,7 @@
         <v>178</v>
       </c>
       <c r="F676">
-        <v>4.7080000000000002</v>
+        <v>4.28</v>
       </c>
       <c r="G676">
         <v>4</v>
@@ -25475,7 +25475,7 @@
         <v>167</v>
       </c>
       <c r="F677">
-        <v>4.7080000000000002</v>
+        <v>4.28</v>
       </c>
       <c r="G677">
         <v>4</v>
@@ -25510,7 +25510,7 @@
         <v>572</v>
       </c>
       <c r="F678">
-        <v>7.1769999999999996</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="679" spans="1:11" x14ac:dyDescent="0.3">
@@ -25530,7 +25530,7 @@
         <v>538</v>
       </c>
       <c r="F679">
-        <v>7.1769999999999996</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="680" spans="1:11" x14ac:dyDescent="0.3">
@@ -25550,7 +25550,7 @@
         <v>573</v>
       </c>
       <c r="F680">
-        <v>7.1769999999999996</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="681" spans="1:11" x14ac:dyDescent="0.3">
@@ -25570,7 +25570,7 @@
         <v>352</v>
       </c>
       <c r="F681">
-        <v>7.1769999999999996</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="682" spans="1:11" x14ac:dyDescent="0.3">
@@ -25590,7 +25590,7 @@
         <v>574</v>
       </c>
       <c r="F682">
-        <v>7.1769999999999996</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="683" spans="1:11" x14ac:dyDescent="0.3">
@@ -25610,7 +25610,7 @@
         <v>575</v>
       </c>
       <c r="F683">
-        <v>5.1120000000000001</v>
+        <v>5.2759999999999998</v>
       </c>
       <c r="G683">
         <v>5</v>
@@ -25645,7 +25645,7 @@
         <v>576</v>
       </c>
       <c r="F684">
-        <v>2.2040000000000002</v>
+        <v>2.0539999999999998</v>
       </c>
       <c r="G684">
         <v>3</v>
@@ -25680,7 +25680,7 @@
         <v>80</v>
       </c>
       <c r="F685">
-        <v>2.2040000000000002</v>
+        <v>2.0539999999999998</v>
       </c>
       <c r="G685">
         <v>3</v>
@@ -25715,7 +25715,7 @@
         <v>37</v>
       </c>
       <c r="F686">
-        <v>2.2040000000000002</v>
+        <v>2.0539999999999998</v>
       </c>
       <c r="G686">
         <v>3</v>
@@ -25750,7 +25750,7 @@
         <v>80</v>
       </c>
       <c r="F687">
-        <v>2.2040000000000002</v>
+        <v>2.0539999999999998</v>
       </c>
       <c r="G687">
         <v>3</v>
@@ -25785,7 +25785,7 @@
         <v>73</v>
       </c>
       <c r="F688">
-        <v>2.609</v>
+        <v>2.6779999999999999</v>
       </c>
       <c r="G688">
         <v>3</v>
@@ -25820,7 +25820,7 @@
         <v>577</v>
       </c>
       <c r="F689">
-        <v>8.1590000000000007</v>
+        <v>8.3330000000000002</v>
       </c>
       <c r="G689">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>101</v>
       </c>
       <c r="F690">
-        <v>2.0350000000000001</v>
+        <v>2.1509999999999998</v>
       </c>
       <c r="G690">
         <v>3</v>
@@ -25884,7 +25884,7 @@
         <v>578</v>
       </c>
       <c r="F691">
-        <v>2.0350000000000001</v>
+        <v>2.1509999999999998</v>
       </c>
       <c r="G691">
         <v>3</v>
@@ -25919,7 +25919,7 @@
         <v>51</v>
       </c>
       <c r="F692">
-        <v>2.0350000000000001</v>
+        <v>2.1509999999999998</v>
       </c>
       <c r="G692">
         <v>3</v>
@@ -25954,7 +25954,7 @@
         <v>579</v>
       </c>
       <c r="F693">
-        <v>5.3460000000000001</v>
+        <v>5.2869999999999999</v>
       </c>
       <c r="G693">
         <v>9</v>
@@ -25989,7 +25989,7 @@
         <v>579</v>
       </c>
       <c r="F694">
-        <v>5.3460000000000001</v>
+        <v>5.2869999999999999</v>
       </c>
       <c r="G694">
         <v>9</v>
@@ -26024,7 +26024,7 @@
         <v>173</v>
       </c>
       <c r="F695">
-        <v>5.3460000000000001</v>
+        <v>5.2869999999999999</v>
       </c>
       <c r="G695">
         <v>9</v>
@@ -26059,7 +26059,7 @@
         <v>580</v>
       </c>
       <c r="F696">
-        <v>6.125</v>
+        <v>6.1550000000000002</v>
       </c>
       <c r="G696">
         <v>6</v>
@@ -26091,7 +26091,7 @@
         <v>581</v>
       </c>
       <c r="F697">
-        <v>7.5259999999999998</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="698" spans="1:11" x14ac:dyDescent="0.3">
@@ -26111,7 +26111,7 @@
         <v>430</v>
       </c>
       <c r="F698">
-        <v>7.5259999999999998</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="699" spans="1:11" x14ac:dyDescent="0.3">
@@ -26131,7 +26131,7 @@
         <v>33</v>
       </c>
       <c r="F699">
-        <v>1.7010000000000001</v>
+        <v>1.6779999999999999</v>
       </c>
       <c r="G699">
         <v>2</v>
@@ -26166,7 +26166,7 @@
         <v>43</v>
       </c>
       <c r="F700">
-        <v>1.7010000000000001</v>
+        <v>1.6779999999999999</v>
       </c>
       <c r="G700">
         <v>2</v>
@@ -26201,7 +26201,7 @@
         <v>582</v>
       </c>
       <c r="F701">
-        <v>1.7010000000000001</v>
+        <v>1.6779999999999999</v>
       </c>
       <c r="G701">
         <v>2</v>
@@ -26236,7 +26236,7 @@
         <v>73</v>
       </c>
       <c r="F702">
-        <v>1.7010000000000001</v>
+        <v>1.6779999999999999</v>
       </c>
       <c r="G702">
         <v>2</v>
@@ -26271,7 +26271,7 @@
         <v>101</v>
       </c>
       <c r="F703">
-        <v>1.7010000000000001</v>
+        <v>1.6779999999999999</v>
       </c>
       <c r="G703">
         <v>2</v>
@@ -26306,7 +26306,7 @@
         <v>325</v>
       </c>
       <c r="F704">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G704">
         <v>6</v>
@@ -26341,7 +26341,7 @@
         <v>153</v>
       </c>
       <c r="F705">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G705">
         <v>6</v>
@@ -26376,7 +26376,7 @@
         <v>583</v>
       </c>
       <c r="F706">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G706">
         <v>6</v>
@@ -26411,7 +26411,7 @@
         <v>583</v>
       </c>
       <c r="F707">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G707">
         <v>6</v>
@@ -26446,7 +26446,7 @@
         <v>584</v>
       </c>
       <c r="F708">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G708">
         <v>6</v>
@@ -26481,7 +26481,7 @@
         <v>585</v>
       </c>
       <c r="F709">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G709">
         <v>6</v>
@@ -26516,7 +26516,7 @@
         <v>586</v>
       </c>
       <c r="F710">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G710">
         <v>6</v>
@@ -26551,7 +26551,7 @@
         <v>325</v>
       </c>
       <c r="F711">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G711">
         <v>6</v>
@@ -26586,7 +26586,7 @@
         <v>325</v>
       </c>
       <c r="F712">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G712">
         <v>6</v>
@@ -26621,7 +26621,7 @@
         <v>585</v>
       </c>
       <c r="F713">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G713">
         <v>6</v>
@@ -26656,7 +26656,7 @@
         <v>153</v>
       </c>
       <c r="F714">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G714">
         <v>6</v>
@@ -26691,7 +26691,7 @@
         <v>325</v>
       </c>
       <c r="F715">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G715">
         <v>6</v>
@@ -26726,7 +26726,7 @@
         <v>325</v>
       </c>
       <c r="F716">
-        <v>4.6459999999999999</v>
+        <v>4.548</v>
       </c>
       <c r="G716">
         <v>6</v>
@@ -26761,7 +26761,7 @@
         <v>587</v>
       </c>
       <c r="F717">
-        <v>6.6459999999999999</v>
+        <v>6.6130000000000004</v>
       </c>
       <c r="G717">
         <v>5</v>
@@ -26796,7 +26796,7 @@
         <v>588</v>
       </c>
       <c r="F718">
-        <v>6.6459999999999999</v>
+        <v>6.6130000000000004</v>
       </c>
       <c r="G718">
         <v>5</v>
@@ -26831,7 +26831,7 @@
         <v>149</v>
       </c>
       <c r="F719">
-        <v>6.6989999999999998</v>
+        <v>6.7229999999999999</v>
       </c>
       <c r="G719">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>491</v>
       </c>
       <c r="F720">
-        <v>6.6989999999999998</v>
+        <v>6.6559999999999997</v>
       </c>
       <c r="G720">
         <v>8</v>
@@ -26895,7 +26895,7 @@
         <v>589</v>
       </c>
       <c r="F721">
-        <v>2.3889999999999998</v>
+        <v>2.5379999999999998</v>
       </c>
       <c r="G721">
         <v>4</v>
@@ -26930,7 +26930,7 @@
         <v>59</v>
       </c>
       <c r="F722">
-        <v>2.3889999999999998</v>
+        <v>2.5379999999999998</v>
       </c>
       <c r="G722">
         <v>4</v>
@@ -26965,7 +26965,7 @@
         <v>64</v>
       </c>
       <c r="F723">
-        <v>2.3889999999999998</v>
+        <v>2.5379999999999998</v>
       </c>
       <c r="G723">
         <v>4</v>
@@ -27000,7 +27000,7 @@
         <v>64</v>
       </c>
       <c r="F724">
-        <v>2.3889999999999998</v>
+        <v>2.5379999999999998</v>
       </c>
       <c r="G724">
         <v>4</v>
@@ -27035,7 +27035,7 @@
         <v>303</v>
       </c>
       <c r="F725">
-        <v>4.3879999999999999</v>
+        <v>4.4690000000000003</v>
       </c>
       <c r="G725">
         <v>7</v>
@@ -27070,7 +27070,7 @@
         <v>590</v>
       </c>
       <c r="F726">
-        <v>5.6820000000000004</v>
+        <v>5.8330000000000002</v>
       </c>
       <c r="G726">
         <v>8</v>
@@ -27105,7 +27105,7 @@
         <v>591</v>
       </c>
       <c r="F727">
-        <v>5.6820000000000004</v>
+        <v>5.8330000000000002</v>
       </c>
       <c r="G727">
         <v>8</v>
@@ -27140,7 +27140,7 @@
         <v>592</v>
       </c>
       <c r="F728">
-        <v>5.6820000000000004</v>
+        <v>5.8330000000000002</v>
       </c>
       <c r="G728">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>593</v>
       </c>
       <c r="F729">
-        <v>5.6820000000000004</v>
+        <v>5.8330000000000002</v>
       </c>
       <c r="G729">
         <v>8</v>
@@ -27210,7 +27210,7 @@
         <v>594</v>
       </c>
       <c r="F730">
-        <v>6.5220000000000002</v>
+        <v>6.5049999999999999</v>
       </c>
       <c r="G730">
         <v>7</v>
@@ -27245,7 +27245,7 @@
         <v>551</v>
       </c>
       <c r="F731">
-        <v>3.3730000000000002</v>
+        <v>3.411</v>
       </c>
       <c r="G731">
         <v>3</v>
@@ -27280,7 +27280,7 @@
         <v>73</v>
       </c>
       <c r="F732">
-        <v>3.43</v>
+        <v>3.3679999999999999</v>
       </c>
       <c r="G732">
         <v>6</v>
@@ -27315,7 +27315,7 @@
         <v>73</v>
       </c>
       <c r="F733">
-        <v>3.43</v>
+        <v>3.3679999999999999</v>
       </c>
       <c r="G733">
         <v>6</v>
@@ -27350,7 +27350,7 @@
         <v>73</v>
       </c>
       <c r="F734">
-        <v>3.43</v>
+        <v>3.3679999999999999</v>
       </c>
       <c r="G734">
         <v>6</v>
@@ -27385,7 +27385,7 @@
         <v>73</v>
       </c>
       <c r="F735">
-        <v>3.43</v>
+        <v>3.3679999999999999</v>
       </c>
       <c r="G735">
         <v>6</v>
@@ -27420,7 +27420,7 @@
         <v>325</v>
       </c>
       <c r="F736">
-        <v>3.4860000000000002</v>
+        <v>3.2759999999999998</v>
       </c>
       <c r="G736">
         <v>5</v>
@@ -27455,7 +27455,7 @@
         <v>73</v>
       </c>
       <c r="F737">
-        <v>3.4860000000000002</v>
+        <v>3.2949999999999999</v>
       </c>
       <c r="G737">
         <v>5</v>
@@ -27490,7 +27490,7 @@
         <v>303</v>
       </c>
       <c r="F738">
-        <v>3.391</v>
+        <v>3.5219999999999998</v>
       </c>
       <c r="G738">
         <v>4</v>
@@ -27525,7 +27525,7 @@
         <v>303</v>
       </c>
       <c r="F739">
-        <v>3.391</v>
+        <v>3.5219999999999998</v>
       </c>
       <c r="G739">
         <v>4</v>
@@ -27560,7 +27560,7 @@
         <v>303</v>
       </c>
       <c r="F740">
-        <v>5.9290000000000003</v>
+        <v>6</v>
       </c>
     </row>
     <row r="741" spans="1:11" x14ac:dyDescent="0.3">
@@ -27580,7 +27580,7 @@
         <v>595</v>
       </c>
       <c r="F741">
-        <v>5.4509999999999996</v>
+        <v>5.3979999999999997</v>
       </c>
       <c r="G741">
         <v>6</v>
@@ -27615,7 +27615,7 @@
         <v>343</v>
       </c>
       <c r="F742">
-        <v>5.4509999999999996</v>
+        <v>5.3979999999999997</v>
       </c>
       <c r="G742">
         <v>6</v>
@@ -27650,7 +27650,7 @@
         <v>303</v>
       </c>
       <c r="F743">
-        <v>6.2649999999999997</v>
+        <v>6.2370000000000001</v>
       </c>
       <c r="G743">
         <v>7</v>
@@ -27685,7 +27685,7 @@
         <v>78</v>
       </c>
       <c r="F744">
-        <v>6.2649999999999997</v>
+        <v>6.2370000000000001</v>
       </c>
       <c r="G744">
         <v>7</v>
@@ -27720,7 +27720,7 @@
         <v>596</v>
       </c>
       <c r="F745">
-        <v>5.4909999999999997</v>
+        <v>5.4219999999999997</v>
       </c>
       <c r="G745">
         <v>6</v>
@@ -27755,7 +27755,7 @@
         <v>145</v>
       </c>
       <c r="F746">
-        <v>5.4909999999999997</v>
+        <v>5.4219999999999997</v>
       </c>
       <c r="G746">
         <v>6</v>
@@ -27790,7 +27790,7 @@
         <v>597</v>
       </c>
       <c r="F747">
-        <v>5.4909999999999997</v>
+        <v>5.4219999999999997</v>
       </c>
       <c r="G747">
         <v>6</v>
@@ -27825,7 +27825,7 @@
         <v>598</v>
       </c>
       <c r="F748">
-        <v>5.4909999999999997</v>
+        <v>5.4219999999999997</v>
       </c>
       <c r="G748">
         <v>6</v>
@@ -27860,7 +27860,7 @@
         <v>497</v>
       </c>
       <c r="F749">
-        <v>5.4909999999999997</v>
+        <v>5.4219999999999997</v>
       </c>
       <c r="G749">
         <v>6</v>
@@ -27895,7 +27895,7 @@
         <v>508</v>
       </c>
       <c r="F750">
-        <v>5.4909999999999997</v>
+        <v>5.4219999999999997</v>
       </c>
       <c r="G750">
         <v>6</v>
@@ -27930,7 +27930,7 @@
         <v>531</v>
       </c>
       <c r="F751">
-        <v>5.4909999999999997</v>
+        <v>5.4219999999999997</v>
       </c>
       <c r="G751">
         <v>6</v>
@@ -27965,7 +27965,7 @@
         <v>599</v>
       </c>
       <c r="F752">
-        <v>4.6280000000000001</v>
+        <v>4.6340000000000003</v>
       </c>
       <c r="G752">
         <v>6</v>
@@ -28000,7 +28000,7 @@
         <v>559</v>
       </c>
       <c r="F753">
-        <v>4.6280000000000001</v>
+        <v>4.6340000000000003</v>
       </c>
       <c r="G753">
         <v>6</v>
@@ -28035,7 +28035,7 @@
         <v>209</v>
       </c>
       <c r="F754">
-        <v>6.76</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="755" spans="1:11" x14ac:dyDescent="0.3">
@@ -28055,7 +28055,7 @@
         <v>145</v>
       </c>
       <c r="F755">
-        <v>5.274</v>
+        <v>5.1289999999999996</v>
       </c>
       <c r="G755">
         <v>5</v>
@@ -28090,7 +28090,7 @@
         <v>144</v>
       </c>
       <c r="F756">
-        <v>5.274</v>
+        <v>5.0110000000000001</v>
       </c>
       <c r="G756">
         <v>5</v>
@@ -28125,7 +28125,7 @@
         <v>600</v>
       </c>
       <c r="F757">
-        <v>3.0270000000000001</v>
+        <v>2.9460000000000002</v>
       </c>
       <c r="G757">
         <v>3</v>
@@ -28160,7 +28160,7 @@
         <v>325</v>
       </c>
       <c r="F758">
-        <v>4.726</v>
+        <v>4.6929999999999996</v>
       </c>
       <c r="G758">
         <v>5</v>
@@ -28195,7 +28195,7 @@
         <v>73</v>
       </c>
       <c r="F759">
-        <v>4.2060000000000004</v>
+        <v>4.2759999999999998</v>
       </c>
       <c r="G759">
         <v>3</v>
@@ -28230,7 +28230,7 @@
         <v>73</v>
       </c>
       <c r="F760">
-        <v>4.2060000000000004</v>
+        <v>4.2759999999999998</v>
       </c>
       <c r="G760">
         <v>3</v>
@@ -28265,7 +28265,7 @@
         <v>601</v>
       </c>
       <c r="F761">
-        <v>7.1239999999999997</v>
+        <v>7.452</v>
       </c>
       <c r="H761">
         <v>7</v>
@@ -28297,7 +28297,7 @@
         <v>303</v>
       </c>
       <c r="F762">
-        <v>7.1239999999999997</v>
+        <v>7.452</v>
       </c>
       <c r="H762">
         <v>7</v>
@@ -28329,7 +28329,7 @@
         <v>155</v>
       </c>
       <c r="F763">
-        <v>7.1239999999999997</v>
+        <v>7.452</v>
       </c>
       <c r="H763">
         <v>7</v>
@@ -28361,7 +28361,7 @@
         <v>602</v>
       </c>
       <c r="F764">
-        <v>7.1239999999999997</v>
+        <v>7.4160000000000004</v>
       </c>
       <c r="H764">
         <v>7</v>
@@ -28393,7 +28393,7 @@
         <v>603</v>
       </c>
       <c r="F765">
-        <v>7.1239999999999997</v>
+        <v>7.4160000000000004</v>
       </c>
       <c r="H765">
         <v>7</v>
@@ -28425,7 +28425,7 @@
         <v>604</v>
       </c>
       <c r="F766">
-        <v>7.1239999999999997</v>
+        <v>7.452</v>
       </c>
       <c r="H766">
         <v>7</v>
@@ -28457,7 +28457,7 @@
         <v>605</v>
       </c>
       <c r="F767">
-        <v>5.3810000000000002</v>
+        <v>5.3760000000000003</v>
       </c>
       <c r="G767">
         <v>5</v>
@@ -28489,7 +28489,7 @@
         <v>606</v>
       </c>
       <c r="F768">
-        <v>5.3810000000000002</v>
+        <v>5.3760000000000003</v>
       </c>
       <c r="G768">
         <v>5</v>
@@ -28521,7 +28521,7 @@
         <v>607</v>
       </c>
       <c r="F769">
-        <v>6.5659999999999998</v>
+        <v>6.516</v>
       </c>
       <c r="G769">
         <v>6</v>
@@ -28556,7 +28556,7 @@
         <v>608</v>
       </c>
       <c r="F770">
-        <v>6.5659999999999998</v>
+        <v>6.516</v>
       </c>
       <c r="G770">
         <v>6</v>
@@ -28591,7 +28591,7 @@
         <v>609</v>
       </c>
       <c r="F771">
-        <v>3.3980000000000001</v>
+        <v>3.2469999999999999</v>
       </c>
       <c r="G771">
         <v>5</v>
@@ -28626,7 +28626,7 @@
         <v>610</v>
       </c>
       <c r="F772">
-        <v>3.3980000000000001</v>
+        <v>3.2469999999999999</v>
       </c>
       <c r="G772">
         <v>5</v>
@@ -28661,7 +28661,7 @@
         <v>611</v>
       </c>
       <c r="F773">
-        <v>3.6019999999999999</v>
+        <v>3.6240000000000001</v>
       </c>
       <c r="G773">
         <v>6</v>
@@ -28696,7 +28696,7 @@
         <v>612</v>
       </c>
       <c r="F774">
-        <v>3.6019999999999999</v>
+        <v>3.6240000000000001</v>
       </c>
       <c r="G774">
         <v>6</v>
@@ -28731,7 +28731,7 @@
         <v>538</v>
       </c>
       <c r="F775">
-        <v>5.4909999999999997</v>
+        <v>5.3559999999999999</v>
       </c>
       <c r="G775">
         <v>6</v>
@@ -28766,7 +28766,7 @@
         <v>613</v>
       </c>
       <c r="F776">
-        <v>5.4909999999999997</v>
+        <v>5.3559999999999999</v>
       </c>
       <c r="G776">
         <v>6</v>
@@ -28801,7 +28801,7 @@
         <v>495</v>
       </c>
       <c r="F777">
-        <v>5.4909999999999997</v>
+        <v>5.3559999999999999</v>
       </c>
       <c r="G777">
         <v>6</v>
@@ -28836,7 +28836,7 @@
         <v>614</v>
       </c>
       <c r="F778">
-        <v>5.4909999999999997</v>
+        <v>5.3559999999999999</v>
       </c>
       <c r="G778">
         <v>6</v>
@@ -28871,7 +28871,7 @@
         <v>543</v>
       </c>
       <c r="F779">
-        <v>5.2389999999999999</v>
+        <v>5.1180000000000003</v>
       </c>
       <c r="G779">
         <v>7</v>
@@ -28906,7 +28906,7 @@
         <v>190</v>
       </c>
       <c r="F780">
-        <v>5.2389999999999999</v>
+        <v>5.1180000000000003</v>
       </c>
       <c r="G780">
         <v>7</v>
@@ -28941,7 +28941,7 @@
         <v>615</v>
       </c>
       <c r="F781">
-        <v>5.2389999999999999</v>
+        <v>5.1180000000000003</v>
       </c>
       <c r="G781">
         <v>7</v>
@@ -28976,7 +28976,7 @@
         <v>307</v>
       </c>
       <c r="F782">
-        <v>6.673</v>
+        <v>6.5940000000000003</v>
       </c>
       <c r="G782">
         <v>8</v>
@@ -29008,7 +29008,7 @@
         <v>589</v>
       </c>
       <c r="F783">
-        <v>2.9649999999999999</v>
+        <v>3.1509999999999998</v>
       </c>
       <c r="G783">
         <v>4</v>
@@ -29043,7 +29043,7 @@
         <v>64</v>
       </c>
       <c r="F784">
-        <v>2.9649999999999999</v>
+        <v>3.1509999999999998</v>
       </c>
       <c r="G784">
         <v>4</v>
@@ -29078,7 +29078,7 @@
         <v>64</v>
       </c>
       <c r="F785">
-        <v>2.9649999999999999</v>
+        <v>3.1509999999999998</v>
       </c>
       <c r="G785">
         <v>4</v>
@@ -29113,7 +29113,7 @@
         <v>64</v>
       </c>
       <c r="F786">
-        <v>2.9649999999999999</v>
+        <v>3.1509999999999998</v>
       </c>
       <c r="G786">
         <v>4</v>
@@ -29148,7 +29148,7 @@
         <v>616</v>
       </c>
       <c r="F787">
-        <v>2.9649999999999999</v>
+        <v>3.1509999999999998</v>
       </c>
       <c r="G787">
         <v>4</v>
@@ -29183,7 +29183,7 @@
         <v>617</v>
       </c>
       <c r="F788">
-        <v>1.72</v>
+        <v>1.6319999999999999</v>
       </c>
       <c r="G788">
         <v>3</v>
@@ -29218,7 +29218,7 @@
         <v>107</v>
       </c>
       <c r="F789">
-        <v>5.6020000000000003</v>
+        <v>5.6449999999999996</v>
       </c>
     </row>
     <row r="790" spans="1:11" x14ac:dyDescent="0.3">
@@ -29238,7 +29238,7 @@
         <v>399</v>
       </c>
       <c r="F790">
-        <v>5.6020000000000003</v>
+        <v>5.6449999999999996</v>
       </c>
     </row>
     <row r="791" spans="1:11" x14ac:dyDescent="0.3">
@@ -29258,7 +29258,7 @@
         <v>399</v>
       </c>
       <c r="F791">
-        <v>5.6020000000000003</v>
+        <v>5.6449999999999996</v>
       </c>
     </row>
     <row r="792" spans="1:11" x14ac:dyDescent="0.3">
@@ -29278,7 +29278,7 @@
         <v>618</v>
       </c>
       <c r="F792">
-        <v>5.6020000000000003</v>
+        <v>5.6449999999999996</v>
       </c>
     </row>
     <row r="793" spans="1:11" x14ac:dyDescent="0.3">
@@ -29298,7 +29298,7 @@
         <v>619</v>
       </c>
       <c r="F793">
-        <v>5.6020000000000003</v>
+        <v>5.6340000000000003</v>
       </c>
     </row>
     <row r="794" spans="1:11" x14ac:dyDescent="0.3">
@@ -29318,7 +29318,7 @@
         <v>495</v>
       </c>
       <c r="F794">
-        <v>5.9829999999999997</v>
+        <v>5.875</v>
       </c>
       <c r="G794">
         <v>7</v>
@@ -29353,7 +29353,7 @@
         <v>190</v>
       </c>
       <c r="F795">
-        <v>5.9829999999999997</v>
+        <v>5.875</v>
       </c>
       <c r="G795">
         <v>7</v>
@@ -29388,7 +29388,7 @@
         <v>191</v>
       </c>
       <c r="F796">
-        <v>5.9829999999999997</v>
+        <v>5.875</v>
       </c>
       <c r="G796">
         <v>7</v>
@@ -29423,7 +29423,7 @@
         <v>192</v>
       </c>
       <c r="F797">
-        <v>5.9829999999999997</v>
+        <v>5.875</v>
       </c>
       <c r="G797">
         <v>7</v>
@@ -29458,7 +29458,7 @@
         <v>620</v>
       </c>
       <c r="F798">
-        <v>2.794</v>
+        <v>2.7930000000000001</v>
       </c>
       <c r="G798">
         <v>5</v>
@@ -29493,7 +29493,7 @@
         <v>621</v>
       </c>
       <c r="F799">
-        <v>4.1950000000000003</v>
+        <v>4.3010000000000002</v>
       </c>
       <c r="G799">
         <v>5</v>
@@ -29528,7 +29528,7 @@
         <v>622</v>
       </c>
       <c r="F800">
-        <v>6.1210000000000004</v>
+        <v>6.1879999999999997</v>
       </c>
     </row>
     <row r="801" spans="1:11" x14ac:dyDescent="0.3">
@@ -29548,7 +29548,7 @@
         <v>623</v>
       </c>
       <c r="F801">
-        <v>3.7879999999999998</v>
+        <v>3.806</v>
       </c>
       <c r="G801">
         <v>3</v>
@@ -29583,7 +29583,7 @@
         <v>624</v>
       </c>
       <c r="F802">
-        <v>3.7879999999999998</v>
+        <v>3.806</v>
       </c>
       <c r="G802">
         <v>3</v>
@@ -29618,7 +29618,7 @@
         <v>178</v>
       </c>
       <c r="F803">
-        <v>1.7569999999999999</v>
+        <v>1.7470000000000001</v>
       </c>
       <c r="G803">
         <v>4</v>
@@ -29653,7 +29653,7 @@
         <v>164</v>
       </c>
       <c r="F804">
-        <v>1.7569999999999999</v>
+        <v>1.7470000000000001</v>
       </c>
       <c r="G804">
         <v>4</v>
@@ -29688,7 +29688,7 @@
         <v>625</v>
       </c>
       <c r="F805">
-        <v>4.0750000000000002</v>
+        <v>4.1840000000000002</v>
       </c>
       <c r="G805">
         <v>5</v>
@@ -29723,7 +29723,7 @@
         <v>626</v>
       </c>
       <c r="F806">
-        <v>4.0750000000000002</v>
+        <v>4.1840000000000002</v>
       </c>
       <c r="G806">
         <v>5</v>
@@ -29758,7 +29758,7 @@
         <v>627</v>
       </c>
       <c r="F807">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="G807">
         <v>6</v>
@@ -29793,7 +29793,7 @@
         <v>453</v>
       </c>
       <c r="F808">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="G808">
         <v>6</v>
@@ -29828,7 +29828,7 @@
         <v>628</v>
       </c>
       <c r="F809">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="G809">
         <v>6</v>
@@ -29863,7 +29863,7 @@
         <v>629</v>
       </c>
       <c r="F810">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="G810">
         <v>6</v>
@@ -29898,7 +29898,7 @@
         <v>630</v>
       </c>
       <c r="F811">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="G811">
         <v>6</v>
@@ -29933,7 +29933,7 @@
         <v>631</v>
       </c>
       <c r="F812">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="G812">
         <v>6</v>
@@ -29968,7 +29968,7 @@
         <v>598</v>
       </c>
       <c r="F813">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="G813">
         <v>6</v>
@@ -30003,7 +30003,7 @@
         <v>632</v>
       </c>
       <c r="F814">
-        <v>3.2269999999999999</v>
+        <v>3.278</v>
       </c>
       <c r="G814">
         <v>5</v>
@@ -30038,7 +30038,7 @@
         <v>319</v>
       </c>
       <c r="F815">
-        <v>5.69</v>
+        <v>5.7530000000000001</v>
       </c>
       <c r="G815">
         <v>5</v>
@@ -30073,7 +30073,7 @@
         <v>634</v>
       </c>
       <c r="F816">
-        <v>7.29</v>
+        <v>7.3330000000000002</v>
       </c>
     </row>
     <row r="817" spans="1:11" x14ac:dyDescent="0.3">
@@ -30093,7 +30093,7 @@
         <v>280</v>
       </c>
       <c r="F817">
-        <v>2.0270000000000001</v>
+        <v>2.0750000000000002</v>
       </c>
       <c r="G817">
         <v>3</v>
@@ -30128,7 +30128,7 @@
         <v>635</v>
       </c>
       <c r="F818">
-        <v>5.5919999999999996</v>
+        <v>5.6920000000000002</v>
       </c>
       <c r="G818">
         <v>5</v>
@@ -30163,7 +30163,7 @@
         <v>636</v>
       </c>
       <c r="F819">
-        <v>5.5919999999999996</v>
+        <v>5.6920000000000002</v>
       </c>
       <c r="G819">
         <v>5</v>
@@ -30198,7 +30198,7 @@
         <v>552</v>
       </c>
       <c r="F820">
-        <v>4.5979999999999999</v>
+        <v>4.4829999999999997</v>
       </c>
       <c r="G820">
         <v>5</v>
@@ -30233,7 +30233,7 @@
         <v>637</v>
       </c>
       <c r="F821">
-        <v>4.5979999999999999</v>
+        <v>4.4829999999999997</v>
       </c>
       <c r="G821">
         <v>5</v>
@@ -30268,7 +30268,7 @@
         <v>638</v>
       </c>
       <c r="F822">
-        <v>4.5979999999999999</v>
+        <v>4.4829999999999997</v>
       </c>
       <c r="G822">
         <v>5</v>
@@ -30303,7 +30303,7 @@
         <v>639</v>
       </c>
       <c r="F823">
-        <v>4.5979999999999999</v>
+        <v>4.4829999999999997</v>
       </c>
       <c r="G823">
         <v>5</v>
@@ -30338,7 +30338,7 @@
         <v>640</v>
       </c>
       <c r="F824">
-        <v>6.8140000000000001</v>
+        <v>7.0540000000000003</v>
       </c>
     </row>
     <row r="825" spans="1:11" x14ac:dyDescent="0.3">
@@ -30358,7 +30358,7 @@
         <v>599</v>
       </c>
       <c r="F825">
-        <v>4.0709999999999997</v>
+        <v>4.0860000000000003</v>
       </c>
       <c r="G825">
         <v>4</v>
@@ -30393,7 +30393,7 @@
         <v>641</v>
       </c>
       <c r="F826">
-        <v>4.0709999999999997</v>
+        <v>4.0860000000000003</v>
       </c>
       <c r="G826">
         <v>4</v>
@@ -30428,7 +30428,7 @@
         <v>107</v>
       </c>
       <c r="F827">
-        <v>6.4909999999999997</v>
+        <v>6.4269999999999996</v>
       </c>
       <c r="G827">
         <v>7</v>
@@ -30460,7 +30460,7 @@
         <v>642</v>
       </c>
       <c r="F828">
-        <v>6.4909999999999997</v>
+        <v>6.4269999999999996</v>
       </c>
       <c r="G828">
         <v>7</v>
@@ -30492,7 +30492,7 @@
         <v>643</v>
       </c>
       <c r="F829">
-        <v>6.4909999999999997</v>
+        <v>6.4269999999999996</v>
       </c>
       <c r="G829">
         <v>7</v>
@@ -30524,7 +30524,7 @@
         <v>107</v>
       </c>
       <c r="F830">
-        <v>6.4909999999999997</v>
+        <v>6.4269999999999996</v>
       </c>
       <c r="G830">
         <v>7</v>
@@ -30556,7 +30556,7 @@
         <v>644</v>
       </c>
       <c r="F831">
-        <v>6.4909999999999997</v>
+        <v>6.4269999999999996</v>
       </c>
       <c r="G831">
         <v>7</v>
@@ -30588,7 +30588,7 @@
         <v>431</v>
       </c>
       <c r="F832">
-        <v>6.4909999999999997</v>
+        <v>6.4269999999999996</v>
       </c>
       <c r="G832">
         <v>7</v>
@@ -30620,7 +30620,7 @@
         <v>147</v>
       </c>
       <c r="F833">
-        <v>6.4909999999999997</v>
+        <v>6.4269999999999996</v>
       </c>
       <c r="G833">
         <v>7</v>
@@ -30652,7 +30652,7 @@
         <v>531</v>
       </c>
       <c r="F834">
-        <v>6.4909999999999997</v>
+        <v>6.4269999999999996</v>
       </c>
       <c r="G834">
         <v>7</v>
@@ -30684,7 +30684,7 @@
         <v>645</v>
       </c>
       <c r="F835">
-        <v>4.1779999999999999</v>
+        <v>4.1260000000000003</v>
       </c>
       <c r="G835">
         <v>4</v>
@@ -30719,7 +30719,7 @@
         <v>646</v>
       </c>
       <c r="F836">
-        <v>5.4420000000000002</v>
+        <v>5.4729999999999999</v>
       </c>
       <c r="G836">
         <v>6</v>
@@ -30754,7 +30754,7 @@
         <v>151</v>
       </c>
       <c r="F837">
-        <v>5.4420000000000002</v>
+        <v>5.4729999999999999</v>
       </c>
       <c r="G837">
         <v>6</v>
@@ -30789,7 +30789,7 @@
         <v>73</v>
       </c>
       <c r="F838">
-        <v>3.2429999999999999</v>
+        <v>3.3679999999999999</v>
       </c>
       <c r="G838">
         <v>4</v>
@@ -30824,7 +30824,7 @@
         <v>73</v>
       </c>
       <c r="F839">
-        <v>3.2429999999999999</v>
+        <v>3.3679999999999999</v>
       </c>
       <c r="G839">
         <v>4</v>
@@ -30859,7 +30859,7 @@
         <v>73</v>
       </c>
       <c r="F840">
-        <v>3.2429999999999999</v>
+        <v>3.3679999999999999</v>
       </c>
       <c r="G840">
         <v>4</v>
@@ -30894,7 +30894,7 @@
         <v>73</v>
       </c>
       <c r="F841">
-        <v>3.2429999999999999</v>
+        <v>3.3679999999999999</v>
       </c>
       <c r="G841">
         <v>4</v>
@@ -30929,7 +30929,7 @@
         <v>307</v>
       </c>
       <c r="F842">
-        <v>4.867</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="843" spans="1:11" x14ac:dyDescent="0.3">
@@ -30949,7 +30949,7 @@
         <v>647</v>
       </c>
       <c r="F843">
-        <v>3.6640000000000001</v>
+        <v>3.6339999999999999</v>
       </c>
       <c r="G843">
         <v>3</v>
@@ -30984,7 +30984,7 @@
         <v>648</v>
       </c>
       <c r="F844">
-        <v>1.776</v>
+        <v>1.8620000000000001</v>
       </c>
       <c r="G844">
         <v>3</v>
@@ -31019,7 +31019,7 @@
         <v>280</v>
       </c>
       <c r="F845">
-        <v>2.6190000000000002</v>
+        <v>2.5590000000000002</v>
       </c>
       <c r="G845">
         <v>2</v>
@@ -31054,7 +31054,7 @@
         <v>280</v>
       </c>
       <c r="F846">
-        <v>2.6190000000000002</v>
+        <v>2.5590000000000002</v>
       </c>
       <c r="G846">
         <v>2</v>
@@ -31089,7 +31089,7 @@
         <v>12</v>
       </c>
       <c r="F847">
-        <v>2.6190000000000002</v>
+        <v>2.5590000000000002</v>
       </c>
       <c r="G847">
         <v>2</v>
@@ -31124,7 +31124,7 @@
         <v>12</v>
       </c>
       <c r="F848">
-        <v>2.6190000000000002</v>
+        <v>2.5590000000000002</v>
       </c>
       <c r="G848">
         <v>2</v>
@@ -31159,7 +31159,7 @@
         <v>649</v>
       </c>
       <c r="F849">
-        <v>1.909</v>
+        <v>1.8440000000000001</v>
       </c>
       <c r="G849">
         <v>3</v>
@@ -31194,7 +31194,7 @@
         <v>337</v>
       </c>
       <c r="F850">
-        <v>1.909</v>
+        <v>1.8440000000000001</v>
       </c>
       <c r="G850">
         <v>3</v>
@@ -31229,7 +31229,7 @@
         <v>650</v>
       </c>
       <c r="F851">
-        <v>4.3719999999999999</v>
+        <v>4.43</v>
       </c>
       <c r="G851">
         <v>4</v>
@@ -31264,7 +31264,7 @@
         <v>73</v>
       </c>
       <c r="F852">
-        <v>3.7269999999999999</v>
+        <v>3.7559999999999998</v>
       </c>
       <c r="G852">
         <v>5</v>
@@ -31299,7 +31299,7 @@
         <v>73</v>
       </c>
       <c r="F853">
-        <v>3.7269999999999999</v>
+        <v>3.7559999999999998</v>
       </c>
       <c r="G853">
         <v>5</v>
@@ -31334,7 +31334,7 @@
         <v>153</v>
       </c>
       <c r="F854">
-        <v>4.8559999999999999</v>
+        <v>4.5119999999999996</v>
       </c>
       <c r="G854">
         <v>7</v>
@@ -31369,7 +31369,7 @@
         <v>153</v>
       </c>
       <c r="F855">
-        <v>4.8559999999999999</v>
+        <v>4.5119999999999996</v>
       </c>
       <c r="G855">
         <v>7</v>
@@ -31404,7 +31404,7 @@
         <v>303</v>
       </c>
       <c r="F856">
-        <v>4.8559999999999999</v>
+        <v>4.5119999999999996</v>
       </c>
       <c r="G856">
         <v>7</v>
@@ -31439,7 +31439,7 @@
         <v>145</v>
       </c>
       <c r="F857">
-        <v>6.6369999999999996</v>
+        <v>6.8120000000000003</v>
       </c>
       <c r="G857">
         <v>7</v>
@@ -31471,7 +31471,7 @@
         <v>651</v>
       </c>
       <c r="F858">
-        <v>6.6369999999999996</v>
+        <v>6.8390000000000004</v>
       </c>
       <c r="G858">
         <v>7</v>
@@ -31503,7 +31503,7 @@
         <v>621</v>
       </c>
       <c r="F859">
-        <v>8.5</v>
+        <v>8.4809999999999999</v>
       </c>
     </row>
     <row r="860" spans="1:11" x14ac:dyDescent="0.3">
@@ -31523,7 +31523,7 @@
         <v>602</v>
       </c>
       <c r="F860">
-        <v>8.5</v>
+        <v>8.4380000000000006</v>
       </c>
     </row>
     <row r="861" spans="1:11" x14ac:dyDescent="0.3">
@@ -31543,7 +31543,7 @@
         <v>457</v>
       </c>
       <c r="F861">
-        <v>5.907</v>
+        <v>5.8390000000000004</v>
       </c>
       <c r="G861">
         <v>6</v>
@@ -31578,7 +31578,7 @@
         <v>652</v>
       </c>
       <c r="F862">
-        <v>7.2549999999999999</v>
+        <v>7.2949999999999999</v>
       </c>
     </row>
     <row r="863" spans="1:11" x14ac:dyDescent="0.3">
@@ -31598,7 +31598,7 @@
         <v>653</v>
       </c>
       <c r="F863">
-        <v>6.2389999999999999</v>
+        <v>6.4409999999999998</v>
       </c>
       <c r="G863">
         <v>8</v>
@@ -31630,7 +31630,7 @@
         <v>649</v>
       </c>
       <c r="F864">
-        <v>1.827</v>
+        <v>1.833</v>
       </c>
       <c r="G864">
         <v>1</v>
@@ -31665,7 +31665,7 @@
         <v>654</v>
       </c>
       <c r="F865">
-        <v>4.4909999999999997</v>
+        <v>4.6669999999999998</v>
       </c>
       <c r="G865">
         <v>4</v>
@@ -31700,7 +31700,7 @@
         <v>655</v>
       </c>
       <c r="F866">
-        <v>4.4909999999999997</v>
+        <v>4.6669999999999998</v>
       </c>
       <c r="G866">
         <v>4</v>
@@ -31735,7 +31735,7 @@
         <v>656</v>
       </c>
       <c r="F867">
-        <v>6.1680000000000001</v>
+        <v>6.2039999999999997</v>
       </c>
       <c r="G867">
         <v>7</v>
@@ -31761,7 +31761,7 @@
         <v>658</v>
       </c>
       <c r="F868">
-        <v>6.1680000000000001</v>
+        <v>6.2039999999999997</v>
       </c>
       <c r="G868">
         <v>7</v>
@@ -31787,7 +31787,7 @@
         <v>199</v>
       </c>
       <c r="F869">
-        <v>6.1680000000000001</v>
+        <v>6.2039999999999997</v>
       </c>
       <c r="G869">
         <v>7</v>
